--- a/data/gravel/Doppo by Simworks Ronin 2025.xlsx
+++ b/data/gravel/Doppo by Simworks Ronin 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{607A2D28-4CB0-9847-84F8-4B76119C0F47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921B1753-E8A9-CF47-BFD3-9F148B64E7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7680" yWindow="500" windowWidth="25960" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2840" yWindow="500" windowWidth="25960" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="103">
   <si>
     <t>brand</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>not spec'd</t>
+  </si>
+  <si>
+    <t>https://www.sim.works/cdn/shop/files/DSCF4646_2_720x.jpg?v=1733446292</t>
   </si>
 </sst>
 </file>
@@ -724,6 +727,11 @@
         <v>90</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Doppo by Simworks Ronin 2025.xlsx
+++ b/data/gravel/Doppo by Simworks Ronin 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{921B1753-E8A9-CF47-BFD3-9F148B64E7F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31B78CD-70FB-6941-B7AD-CE6D43EEF1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2840" yWindow="500" windowWidth="25960" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -342,6 +342,12 @@
   </si>
   <si>
     <t>https://www.sim.works/cdn/shop/files/DSCF4646_2_720x.jpg?v=1733446292</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Nagoya, Japan</t>
   </si>
 </sst>
 </file>
@@ -681,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1424,6 +1430,14 @@
         <v>86</v>
       </c>
     </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>103</v>
+      </c>
+      <c r="B72" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Doppo by Simworks Ronin 2025.xlsx
+++ b/data/gravel/Doppo by Simworks Ronin 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F31B78CD-70FB-6941-B7AD-CE6D43EEF1E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{835371AA-770B-E246-B401-2A5702D021FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2840" yWindow="500" windowWidth="25960" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,24 @@
   </si>
   <si>
     <t>Nagoya, Japan</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -687,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1271,170 +1289,200 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>43</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>44</v>
+        <v>106</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>45</v>
-      </c>
-      <c r="B50">
-        <v>27.2</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>49</v>
+        <v>43</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>45</v>
+      </c>
+      <c r="B56">
+        <v>27.2</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>99</v>
+        <v>70</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>53</v>
-      </c>
-      <c r="B58" s="2"/>
+        <v>47</v>
+      </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>54</v>
-      </c>
-      <c r="B59" s="2"/>
+        <v>48</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>58</v>
-      </c>
-      <c r="B63" s="2"/>
+        <v>52</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>59</v>
-      </c>
-      <c r="B64">
-        <v>3</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B64" s="2"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>60</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>70</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="B65" s="2"/>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>61</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>62</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>70</v>
+        <v>56</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="B68">
-        <v>2400</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>64</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="B69" s="2"/>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>65</v>
-      </c>
-      <c r="B70" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="B70">
+        <v>3</v>
+      </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>61</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>62</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74">
+        <v>2400</v>
+      </c>
+      <c r="C74" s="2"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>65</v>
+      </c>
+      <c r="B76" s="2"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>66</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>103</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>104</v>
       </c>
     </row>
